--- a/data/trans_orig/P13A_1_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P13A_1_2023-Habitat-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>8646</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -760,27 +760,27 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>23869</t>
+          <t>25214</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20112</t>
+          <t>21166</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25454</t>
+          <t>26776</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -795,27 +795,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>32140</t>
+          <t>33860</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28040</t>
+          <t>29486</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33725</t>
+          <t>35422</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>1562</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>5610</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1585</t>
+          <t>1562</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5685</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,76%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>8646</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>8646</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>8646</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25454</t>
+          <t>26776</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25454</t>
+          <t>26776</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25454</t>
+          <t>26776</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>33725</t>
+          <t>35422</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>33725</t>
+          <t>35422</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>33725</t>
+          <t>35422</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14768</t>
+          <t>14923</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1103,27 +1103,27 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>44141</t>
+          <t>49080</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41424</t>
+          <t>45796</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45187</t>
+          <t>50227</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1138,27 +1138,27 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>58909</t>
+          <t>64003</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56212</t>
+          <t>61010</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59955</t>
+          <t>65150</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3763</t>
+          <t>4431</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3743</t>
+          <t>4140</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14768</t>
+          <t>14923</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14768</t>
+          <t>14923</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14768</t>
+          <t>14923</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>45187</t>
+          <t>50227</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>45187</t>
+          <t>50227</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45187</t>
+          <t>50227</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>59955</t>
+          <t>65150</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>59955</t>
+          <t>65150</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>59955</t>
+          <t>65150</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8290</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1446,27 +1446,27 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>31025</t>
+          <t>35968</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28402</t>
+          <t>32614</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31772</t>
+          <t>37488</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1481,27 +1481,27 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>39315</t>
+          <t>46360</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36711</t>
+          <t>42577</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40062</t>
+          <t>47880</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1569,12 +1569,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3370</t>
+          <t>4874</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1604,12 +1604,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>5303</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8290</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8290</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8290</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>31772</t>
+          <t>37488</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31772</t>
+          <t>37488</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31772</t>
+          <t>37488</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>40062</t>
+          <t>47880</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>40062</t>
+          <t>47880</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>40062</t>
+          <t>47880</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6064</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>44459</t>
+          <t>44819</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36373</t>
+          <t>36955</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48126</t>
+          <t>48462</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>50523</t>
+          <t>50767</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41193</t>
+          <t>42352</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54299</t>
+          <t>54485</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4962</t>
+          <t>5056</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13048</t>
+          <t>12920</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4962</t>
+          <t>5056</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1186</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14292</t>
+          <t>13471</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>24,13%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6064</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6064</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6064</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>49421</t>
+          <t>49875</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>49421</t>
+          <t>49875</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>49421</t>
+          <t>49875</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>55485</t>
+          <t>55823</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>55485</t>
+          <t>55823</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>55485</t>
+          <t>55823</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>143494</t>
+          <t>155080</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>134306</t>
+          <t>146218</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>147895</t>
+          <t>159931</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>180887</t>
+          <t>194989</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>171861</t>
+          <t>185120</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>185399</t>
+          <t>199435</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8340</t>
+          <t>9286</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3939</t>
+          <t>4435</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17528</t>
+          <t>18148</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>8340</t>
+          <t>9286</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>4840</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17366</t>
+          <t>19155</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>39908</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>151834</t>
+          <t>164366</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>151834</t>
+          <t>164366</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>151834</t>
+          <t>164366</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>189227</t>
+          <t>204275</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>189227</t>
+          <t>204275</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>189227</t>
+          <t>204275</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
